--- a/data/trans_orig/Q5413-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5413-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2007</t>
+          <t>Población según si es capaz de vestirse solo en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103118</t>
+          <t>102081</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112328</t>
+          <t>112147</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>138347</t>
+          <t>139000</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>148331</t>
+          <t>148385</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>245629</t>
+          <t>245916</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>258654</t>
+          <t>258650</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10197</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132721</t>
+          <t>131050</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142958</t>
+          <t>142929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167105</t>
+          <t>167205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>179311</t>
+          <t>179335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>304710</t>
+          <t>305087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>320899</t>
+          <t>320318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6813</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1933</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6045</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>6791</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6452</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13578</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98439</t>
+          <t>98633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121989</t>
+          <t>122449</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132859</t>
+          <t>132913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>224342</t>
+          <t>223560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>236007</t>
+          <t>235569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>127965</t>
+          <t>128795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135613</t>
+          <t>135580</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191928</t>
+          <t>190326</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203725</t>
+          <t>203490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>322242</t>
+          <t>323039</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>338074</t>
+          <t>338015</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29237</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>25025</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41004</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>472201</t>
+          <t>474818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>489648</t>
+          <t>489784</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>634702</t>
+          <t>634090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>657079</t>
+          <t>656918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1116905</t>
+          <t>1115491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1142557</t>
+          <t>1142066</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2012</t>
+          <t>Población según si es capaz de vestirse solo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21147</t>
+          <t>20356</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26834</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125750</t>
+          <t>125509</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136487</t>
+          <t>136427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>137952</t>
+          <t>137828</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154919</t>
+          <t>154198</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>268423</t>
+          <t>269624</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>289303</t>
+          <t>288191</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28142</t>
+          <t>27326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17205</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>38034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47098</t>
+          <t>48422</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130086</t>
+          <t>130850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145974</t>
+          <t>146303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142625</t>
+          <t>142377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164886</t>
+          <t>164974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>279165</t>
+          <t>278294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307167</t>
+          <t>305683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,27%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>25283</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26945</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29637</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87216</t>
+          <t>88093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100446</t>
+          <t>100539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101132</t>
+          <t>102831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122342</t>
+          <t>122538</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198236</t>
+          <t>196511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>220939</t>
+          <t>220010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>89,94%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23425</t>
+          <t>22702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23379</t>
+          <t>23051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19283</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41248</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>135414</t>
+          <t>136483</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>152965</t>
+          <t>153104</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>209731</t>
+          <t>210570</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>229132</t>
+          <t>228452</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>353189</t>
+          <t>354133</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>378236</t>
+          <t>378152</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26951</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24979</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50207</t>
+          <t>48761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38944</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69020</t>
+          <t>68963</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42030</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56097</t>
+          <t>55221</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>88172</t>
+          <t>88580</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>81175</t>
+          <t>81131</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>120438</t>
+          <t>122333</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>498213</t>
+          <t>499982</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>526656</t>
+          <t>527631</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>615047</t>
+          <t>614708</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>654041</t>
+          <t>654242</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1124043</t>
+          <t>1123798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1172161</t>
+          <t>1172057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2016</t>
+          <t>Población según si es capaz de vestirse solo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23742</t>
+          <t>22676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34499</t>
+          <t>33840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116415</t>
+          <t>115866</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129316</t>
+          <t>128948</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145401</t>
+          <t>146247</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>162445</t>
+          <t>163472</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>267146</t>
+          <t>268507</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>289400</t>
+          <t>289108</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22816</t>
+          <t>23991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29627</t>
+          <t>30652</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151941</t>
+          <t>150810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161531</t>
+          <t>161533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>189873</t>
+          <t>189541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208531</t>
+          <t>208118</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>345371</t>
+          <t>344766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367248</t>
+          <t>367525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22302</t>
+          <t>21702</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>30450</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99773</t>
+          <t>100164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111286</t>
+          <t>111394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112739</t>
+          <t>113176</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130242</t>
+          <t>131422</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217175</t>
+          <t>217524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239445</t>
+          <t>238807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11951</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>23099</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29136</t>
+          <t>30241</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161253</t>
+          <t>161264</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>171526</t>
+          <t>171552</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>215048</t>
+          <t>213728</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>233938</t>
+          <t>233672</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>381164</t>
+          <t>381335</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>402115</t>
+          <t>401528</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33442</t>
+          <t>33367</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40567</t>
+          <t>41615</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38092</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68878</t>
+          <t>70484</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>62430</t>
+          <t>63388</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>99131</t>
+          <t>100240</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>543110</t>
+          <t>543330</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>565254</t>
+          <t>564893</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>685980</t>
+          <t>683371</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>723587</t>
+          <t>721578</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1239059</t>
+          <t>1240059</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1282359</t>
+          <t>1282610</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2023</t>
+          <t>Población según si es capaz de vestirse solo en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>26719</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>22749</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35467</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131401</t>
+          <t>130801</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140847</t>
+          <t>141383</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>149419</t>
+          <t>147930</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160560</t>
+          <t>160149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>284550</t>
+          <t>283085</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>299309</t>
+          <t>298610</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14116</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141691</t>
+          <t>140347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152539</t>
+          <t>151744</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185354</t>
+          <t>184864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198849</t>
+          <t>199057</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>330972</t>
+          <t>330577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>348078</t>
+          <t>348776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21103</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127190</t>
+          <t>127802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135405</t>
+          <t>135426</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>325124</t>
+          <t>327003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357483</t>
+          <t>357036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>464659</t>
+          <t>464513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>492327</t>
+          <t>491923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>13905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34642</t>
+          <t>34481</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>192275</t>
+          <t>192028</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201157</t>
+          <t>200782</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>243731</t>
+          <t>243573</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257749</t>
+          <t>257842</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>439377</t>
+          <t>439486</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>456543</t>
+          <t>455751</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>30414</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38634</t>
+          <t>39311</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37233</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>37155</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86347</t>
+          <t>86836</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>63257</t>
+          <t>57681</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>114125</t>
+          <t>113190</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>604537</t>
+          <t>602981</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>623462</t>
+          <t>623213</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>919854</t>
+          <t>918959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>987599</t>
+          <t>984148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1536595</t>
+          <t>1536618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1600410</t>
+          <t>1609038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5413-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5413-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102081</t>
+          <t>102861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112147</t>
+          <t>112251</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139000</t>
+          <t>139043</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>148385</t>
+          <t>148334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>245916</t>
+          <t>245069</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>258650</t>
+          <t>258740</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131050</t>
+          <t>132597</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142929</t>
+          <t>143006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167205</t>
+          <t>166960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>179335</t>
+          <t>179294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>305087</t>
+          <t>303841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>320318</t>
+          <t>319835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13832</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98633</t>
+          <t>98034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122449</t>
+          <t>122086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132913</t>
+          <t>132872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>223560</t>
+          <t>224858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>235569</t>
+          <t>236091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>13135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>14524</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128795</t>
+          <t>128123</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135580</t>
+          <t>135601</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190326</t>
+          <t>190989</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203490</t>
+          <t>204195</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>323039</t>
+          <t>323626</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>338015</t>
+          <t>338149</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>41035</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>474818</t>
+          <t>472760</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>489784</t>
+          <t>489621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>634090</t>
+          <t>634513</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>656918</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1115491</t>
+          <t>1117009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1142066</t>
+          <t>1143491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20356</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>27359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125509</t>
+          <t>125693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136427</t>
+          <t>136424</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>137828</t>
+          <t>138850</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154198</t>
+          <t>154254</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>269624</t>
+          <t>267630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>288191</t>
+          <t>288181</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13205</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19049</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27326</t>
+          <t>27952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>15923</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>18135</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38034</t>
+          <t>37198</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>24473</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48422</t>
+          <t>48315</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130850</t>
+          <t>129778</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146303</t>
+          <t>145959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142377</t>
+          <t>142505</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164974</t>
+          <t>163870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>278294</t>
+          <t>279522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>305683</t>
+          <t>306280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17070</t>
+          <t>17977</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>27552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30175</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88093</t>
+          <t>86921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100539</t>
+          <t>100511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102831</t>
+          <t>102847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122538</t>
+          <t>123027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196511</t>
+          <t>197870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>220010</t>
+          <t>219925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>15170</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19252</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23051</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39989</t>
+          <t>41559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136483</t>
+          <t>135751</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153104</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>210570</t>
+          <t>210397</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>228452</t>
+          <t>228719</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>354133</t>
+          <t>352645</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>378152</t>
+          <t>377592</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>24560</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>38577</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68963</t>
+          <t>68867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>55221</t>
+          <t>54203</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>88580</t>
+          <t>87175</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>81131</t>
+          <t>82527</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>122333</t>
+          <t>122622</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>499982</t>
+          <t>498251</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>527631</t>
+          <t>526582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>614708</t>
+          <t>617130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>654242</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1123798</t>
+          <t>1126947</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1172057</t>
+          <t>1173560</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22676</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33840</t>
+          <t>34776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115866</t>
+          <t>116217</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>128948</t>
+          <t>129410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146247</t>
+          <t>146645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>163472</t>
+          <t>163283</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>268507</t>
+          <t>267897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>289108</t>
+          <t>289579</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12093</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23991</t>
+          <t>23400</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150810</t>
+          <t>150343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161533</t>
+          <t>161002</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>189541</t>
+          <t>189954</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208118</t>
+          <t>208436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344766</t>
+          <t>346454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367525</t>
+          <t>368107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16481</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>22403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11951</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30450</t>
+          <t>30315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100164</t>
+          <t>100715</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111394</t>
+          <t>111317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113176</t>
+          <t>112422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131422</t>
+          <t>131018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217524</t>
+          <t>217275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238807</t>
+          <t>239387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>13580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30241</t>
+          <t>30222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161264</t>
+          <t>161299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>171552</t>
+          <t>171384</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>213728</t>
+          <t>213972</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>233672</t>
+          <t>233438</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,47 +7401,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>393485</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>379726</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>401736</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>94,27%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>90,97%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>96,25%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>393485</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>381335</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>401528</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41615</t>
+          <t>40932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>38577</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38224</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70484</t>
+          <t>69253</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>63388</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>100240</t>
+          <t>100263</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>543330</t>
+          <t>543780</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>564893</t>
+          <t>565130</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>683371</t>
+          <t>685580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>721578</t>
+          <t>722336</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1240059</t>
+          <t>1239897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1282610</t>
+          <t>1281715</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>15786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26719</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28709</t>
+          <t>30099</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22749</t>
+          <t>23511</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36826</t>
+          <t>37804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>137068</t>
+          <t>151638</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130801</t>
+          <t>145996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141383</t>
+          <t>156139</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>155162</t>
+          <t>165984</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>147930</t>
+          <t>159631</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160149</t>
+          <t>172246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>292229</t>
+          <t>317622</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>283085</t>
+          <t>309004</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>298610</t>
+          <t>325038</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>178690</t>
+          <t>190490</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178690</t>
+          <t>190490</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178690</t>
+          <t>190490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>326773</t>
+          <t>353804</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>326773</t>
+          <t>353804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326773</t>
+          <t>353804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>19661</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>27344</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29154</t>
+          <t>30985</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>23108</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38268</t>
+          <t>39928</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>147740</t>
+          <t>164934</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140347</t>
+          <t>158022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151744</t>
+          <t>169864</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>192405</t>
+          <t>214243</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>184864</t>
+          <t>205472</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>199057</t>
+          <t>220615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>340145</t>
+          <t>379177</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>330577</t>
+          <t>368343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>348776</t>
+          <t>388479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>12913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>132473</t>
+          <t>154749</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127802</t>
+          <t>149518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135426</t>
+          <t>157968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>347167</t>
+          <t>160800</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327003</t>
+          <t>153853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357036</t>
+          <t>165884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>479641</t>
+          <t>315549</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>464513</t>
+          <t>307457</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>491923</t>
+          <t>321978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19445</t>
+          <t>22432</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13905</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26625</t>
+          <t>30573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>29248</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19002</t>
+          <t>21751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34481</t>
+          <t>40324</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>197402</t>
+          <t>207015</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>192028</t>
+          <t>202159</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>200782</t>
+          <t>210775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>251408</t>
+          <t>267892</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>243573</t>
+          <t>259192</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257842</t>
+          <t>274945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>448811</t>
+          <t>474906</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>439486</t>
+          <t>463637</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>455751</t>
+          <t>482878</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30414</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39311</t>
+          <t>38927</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27872</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19970</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>40262</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>65677</t>
+          <t>71194</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>60147</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86836</t>
+          <t>85264</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>93549</t>
+          <t>101205</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>57681</t>
+          <t>87805</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>113190</t>
+          <t>119424</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>614683</t>
+          <t>678336</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>602981</t>
+          <t>667510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>623213</t>
+          <t>687959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>946143</t>
+          <t>808918</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>918959</t>
+          <t>794662</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>984148</t>
+          <t>821183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1560826</t>
+          <t>1487255</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1536618</t>
+          <t>1469476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1609038</t>
+          <t>1504675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1032965</t>
+          <t>902426</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1032965</t>
+          <t>902426</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1032965</t>
+          <t>902426</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1683143</t>
+          <t>1618818</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1683143</t>
+          <t>1618818</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1683143</t>
+          <t>1618818</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
